--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.74264413372427</v>
+      </c>
+      <c r="C2">
         <v>26.10245907677801</v>
-      </c>
-      <c r="C2">
-        <v>26.74264413372427</v>
       </c>
       <c r="D2">
         <v>3.831056671934974</v>
       </c>
       <c r="E2">
-        <v>17.07772020725389</v>
+        <v>17.49656585130738</v>
       </c>
       <c r="F2">
         <v>65.42571394143873</v>
       </c>
       <c r="G2">
-        <v>17.49656585130739</v>
+        <v>17.07772020725389</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>36.09756097560975</v>
+      </c>
+      <c r="C3">
         <v>14.4516946468166</v>
-      </c>
-      <c r="C3">
-        <v>36.09756097560975</v>
       </c>
       <c r="D3">
         <v>6.91960371734175</v>
       </c>
       <c r="E3">
-        <v>9.599313252707853</v>
+        <v>23.97724307992695</v>
       </c>
       <c r="F3">
         <v>66.42344366736519</v>
       </c>
       <c r="G3">
-        <v>23.97724307992695</v>
+        <v>9.599313252707853</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>36.01809954751131</v>
+      </c>
+      <c r="C4">
         <v>22.96631473102061</v>
-      </c>
-      <c r="C4">
-        <v>36.01809954751131</v>
       </c>
       <c r="D4">
         <v>4.354203152364273</v>
       </c>
       <c r="E4">
+        <v>22.65511352855606</v>
+      </c>
+      <c r="F4">
+        <v>62.8992473594333</v>
+      </c>
+      <c r="G4">
         <v>14.44563911201062</v>
-      </c>
-      <c r="F4">
-        <v>62.89924735943331</v>
-      </c>
-      <c r="G4">
-        <v>22.65511352855607</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>41.1864406779661</v>
+      </c>
+      <c r="C5">
         <v>40.67796610169492</v>
-      </c>
-      <c r="C5">
-        <v>41.1864406779661</v>
       </c>
       <c r="D5">
         <v>2.458333333333333</v>
       </c>
       <c r="E5">
-        <v>22.36719478098789</v>
+        <v>22.64678471575023</v>
       </c>
       <c r="F5">
         <v>54.98602050326188</v>
       </c>
       <c r="G5">
-        <v>22.64678471575023</v>
+        <v>22.36719478098788</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>32.36363636363636</v>
+      </c>
+      <c r="C6">
         <v>29.81818181818182</v>
-      </c>
-      <c r="C6">
-        <v>32.36363636363636</v>
       </c>
       <c r="D6">
         <v>3.353658536585366</v>
       </c>
       <c r="E6">
-        <v>18.38565022421524</v>
+        <v>19.95515695067264</v>
       </c>
       <c r="F6">
         <v>61.65919282511211</v>
       </c>
       <c r="G6">
-        <v>19.95515695067264</v>
+        <v>18.38565022421524</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>42.5925925925926</v>
+      </c>
+      <c r="C7">
         <v>33.4610472541507</v>
-      </c>
-      <c r="C7">
-        <v>42.5925925925926</v>
       </c>
       <c r="D7">
         <v>2.988549618320611</v>
       </c>
       <c r="E7">
-        <v>19.00616612259702</v>
+        <v>24.19296336597751</v>
       </c>
       <c r="F7">
         <v>56.80087051142547</v>
       </c>
       <c r="G7">
-        <v>24.19296336597751</v>
+        <v>19.00616612259702</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>35.84594222833562</v>
+      </c>
+      <c r="C8">
         <v>35.6808803301238</v>
-      </c>
-      <c r="C8">
-        <v>35.84594222833562</v>
       </c>
       <c r="D8">
         <v>2.802621434078643</v>
       </c>
       <c r="E8">
-        <v>20.80192461908581</v>
+        <v>20.8981555733761</v>
       </c>
       <c r="F8">
         <v>58.2999198075381</v>
       </c>
       <c r="G8">
-        <v>20.8981555733761</v>
+        <v>20.80192461908581</v>
       </c>
     </row>
   </sheetData>
